--- a/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
@@ -357,31 +357,31 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>**Characteristic**</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>**N = 23,386**</t>
+          <t>N = 22,900</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Age at fracture occurrence</t>
+          <t>Age at Fracture Occurrence</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>70 (61, 81)</t>
+          <t>71 (61, 81)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fracture site</t>
+          <t>Fracture fracture_site</t>
         </is>
       </c>
     </row>
@@ -393,7 +393,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3,173 (14%)</t>
+          <t>3,197 (14%)</t>
         </is>
       </c>
     </row>
@@ -405,7 +405,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1,682 (7.2%)</t>
+          <t>1,699 (7.4%)</t>
         </is>
       </c>
     </row>
@@ -417,129 +417,129 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18,531 (79%)</t>
+          <t>18,004 (79%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Censoring event</t>
+          <t>Censoring Event</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cancer</t>
+          <t>Max of 730 days from index date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>745 (3.2%)</t>
+          <t>9,730 (42%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cancer, Fracture ensuing incident (index) fracture</t>
+          <t>End of Study</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>6,026 (26%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cancer, Paget’s disease of the bone, or other metabolic bone diseases</t>
+          <t>Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>4,071 (18%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Death</t>
+          <t>End of data collection period</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1,266 (5.4%)</t>
+          <t>1,479 (6.5%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>End of data collection period</t>
+          <t>Death</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1,838 (7.9%)</t>
+          <t>1,150 (5.0%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>End of data collection period, Cancer</t>
+          <t>Cancer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>379 (1.7%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
+          <t>Paget’s disease of the bone, or other metabolic bone diseases</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>54 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fracture ensuing incident (index) fracture</t>
+          <t>Max of 730 days from index date, End of Study</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4,036 (17%)</t>
+          <t>7 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date</t>
+          <t>Cancer, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15,411 (66%)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Cancer</t>
+          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -551,12 +551,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, End of data collection period</t>
+          <t>Fracture ensuing incident (index) fracture, End of Study</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2 (&lt;0.1%)</t>
+          <t>1 (&lt;0.1%)</t>
         </is>
       </c>
     </row>
@@ -575,48 +575,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
+          <t>Follow up time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>578 (192, 730)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paget’s disease of the bone, or other metabolic bone diseases</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>78 (0.3%)</t>
+          <t>Heathcare Service User Status</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paget’s disease of the bone, or other metabolic bone diseases, Fracture ensuing incident (index) fracture</t>
+          <t>Non-User</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1 (&lt;0.1%)</t>
+          <t>682 (3.0%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Follow up time</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>730 (365, 730)</t>
+          <t>22,218 (97%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
@@ -381,7 +381,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fracture fracture_site</t>
+          <t>Fracture Site</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Follow up time</t>
+          <t>Follow up Time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">

--- a/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
@@ -1,21 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/Cohort/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_4E70FDCE8F79A8D366075C52F3C03AB736B18345" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73F6509A-D0E4-4171-A3A4-82377A1FB639}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+  <si>
+    <t>**Characteristic**</t>
+  </si>
+  <si>
+    <t>**N = 23,386**</t>
+  </si>
+  <si>
+    <t>Age at fracture occurrence</t>
+  </si>
+  <si>
+    <t>70 (61, 81)</t>
+  </si>
+  <si>
+    <t>Fracture site</t>
+  </si>
+  <si>
+    <t>Hip</t>
+  </si>
+  <si>
+    <t>3,173 (14%)</t>
+  </si>
+  <si>
+    <t>Vertebra</t>
+  </si>
+  <si>
+    <t>1,682 (7.2%)</t>
+  </si>
+  <si>
+    <t>NHNV</t>
+  </si>
+  <si>
+    <t>18,531 (79%)</t>
+  </si>
+  <si>
+    <t>Censoring event</t>
+  </si>
+  <si>
+    <t>Cancer</t>
+  </si>
+  <si>
+    <t>745 (3.2%)</t>
+  </si>
+  <si>
+    <t>Cancer, Fracture ensuing incident (index) fracture</t>
+  </si>
+  <si>
+    <t>2 (&lt;0.1%)</t>
+  </si>
+  <si>
+    <t>Cancer, Paget’s disease of the bone, or other metabolic bone diseases</t>
+  </si>
+  <si>
+    <t>1 (&lt;0.1%)</t>
+  </si>
+  <si>
+    <t>Death</t>
+  </si>
+  <si>
+    <t>1,266 (5.4%)</t>
+  </si>
+  <si>
+    <t>End of data collection period</t>
+  </si>
+  <si>
+    <t>1,838 (7.9%)</t>
+  </si>
+  <si>
+    <t>End of data collection period, Cancer</t>
+  </si>
+  <si>
+    <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
+  </si>
+  <si>
+    <t>Fracture ensuing incident (index) fracture</t>
+  </si>
+  <si>
+    <t>4,036 (17%)</t>
+  </si>
+  <si>
+    <t>Max of 730 days from index date</t>
+  </si>
+  <si>
+    <t>15,411 (66%)</t>
+  </si>
+  <si>
+    <t>Max of 730 days from index date, Cancer</t>
+  </si>
+  <si>
+    <t>Max of 730 days from index date, End of data collection period</t>
+  </si>
+  <si>
+    <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
+  </si>
+  <si>
+    <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
+  </si>
+  <si>
+    <t>Paget’s disease of the bone, or other metabolic bone diseases</t>
+  </si>
+  <si>
+    <t>78 (0.3%)</t>
+  </si>
+  <si>
+    <t>Paget’s disease of the bone, or other metabolic bone diseases, Fracture ensuing incident (index) fracture</t>
+  </si>
+  <si>
+    <t>Follow up time</t>
+  </si>
+  <si>
+    <t>730 (365, 730)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +185,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +237,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +271,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +306,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,274 +482,190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="87.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>**Characteristic**</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>**N = 23,386**</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Age at fracture occurrence</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>70 (61, 81)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Fracture site</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hip</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3,173 (14%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Vertebra</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1,682 (7.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NHNV</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18,531 (79%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Censoring event</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>745 (3.2%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cancer, Fracture ensuing incident (index) fracture</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cancer, Paget’s disease of the bone, or other metabolic bone diseases</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Death</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1,266 (5.4%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>End of data collection period</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1,838 (7.9%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>End of data collection period, Cancer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>End of data collection period, Fracture ensuing incident (index) fracture</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fracture ensuing incident (index) fracture</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>4,036 (17%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Max of 730 days from index date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>15,411 (66%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Max of 730 days from index date, Cancer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Max of 730 days from index date, End of data collection period</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Max of 730 days from index date, Fracture ensuing incident (index) fracture</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Max of 730 days from index date, Paget’s disease of the bone, or other metabolic bone diseases</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Paget’s disease of the bone, or other metabolic bone diseases</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>78 (0.3%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Paget’s disease of the bone, or other metabolic bone diseases, Fracture ensuing incident (index) fracture</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1 (&lt;0.1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Follow up time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>730 (365, 730)</t>
-        </is>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
+++ b/OMOP Analysis/Results/Cohort/Table1_OMOP.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>682 (3.0%)</t>
+          <t>598 (2.6%)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22,218 (97%)</t>
+          <t>22,302 (97%)</t>
         </is>
       </c>
     </row>
